--- a/SGC-CKN/Excel/d393a01e-6b90-4698-ae64-581c932681b7_Cọc_khoan_nhồi_P1-59_D800_01-04-2026.xlsx
+++ b/SGC-CKN/Excel/d393a01e-6b90-4698-ae64-581c932681b7_Cọc_khoan_nhồi_P1-59_D800_01-04-2026.xlsx
@@ -112,7 +112,7 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">08:55
+    <t xml:space="preserve">08:35
 01/04/2026</t>
   </si>
   <si>
@@ -332,11 +332,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
@@ -358,6 +353,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -493,53 +493,53 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1183,190 +1183,190 @@
         <v>-5.2</v>
       </c>
       <c r="H12" s="9">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="I12" s="9">
         <v>3.2</v>
       </c>
-      <c r="J12" s="12">
-        <v>4.8</v>
+      <c r="J12" s="8">
+        <v>9.6</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>-5.2</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-8.5</v>
       </c>
-      <c r="H13" s="13">
-        <v>0.17</v>
-      </c>
-      <c r="I13" s="13">
+      <c r="H13" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="12">
         <v>3.3</v>
       </c>
       <c r="J13" s="8">
-        <v>19.8</v>
-      </c>
-      <c r="K13" s="14" t="s">
+        <v>6.6</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>-8.5</v>
       </c>
-      <c r="G14" s="16">
-        <v>-12.3</v>
-      </c>
-      <c r="H14" s="16">
+      <c r="G14" s="15">
+        <v>-17.3</v>
+      </c>
+      <c r="H14" s="15">
         <v>1.17</v>
       </c>
-      <c r="I14" s="16">
-        <v>3.8</v>
-      </c>
-      <c r="J14" s="12">
-        <v>3.26</v>
-      </c>
-      <c r="K14" s="17" t="s">
+      <c r="I14" s="15">
+        <v>8.8</v>
+      </c>
+      <c r="J14" s="8">
+        <v>7.54</v>
+      </c>
+      <c r="K14" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="19">
-        <v>-12.3</v>
-      </c>
-      <c r="G15" s="19">
+      <c r="F15" s="18">
+        <v>-17.3</v>
+      </c>
+      <c r="G15" s="18">
         <v>-22.5</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <v>0.58</v>
       </c>
-      <c r="I15" s="19">
-        <v>10.2</v>
+      <c r="I15" s="18">
+        <v>5.2</v>
       </c>
       <c r="J15" s="8">
-        <v>17.49</v>
-      </c>
-      <c r="K15" s="20" t="s">
+        <v>8.91</v>
+      </c>
+      <c r="K15" s="19" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="21">
         <v>-22.5</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="21">
         <v>-26.5</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="21">
         <v>0.75</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="21">
         <v>4</v>
       </c>
       <c r="J16" s="8">
         <v>5.33</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="22" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <v>-26.5</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="24">
         <v>-38.2</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="24">
         <v>2.83</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="24">
         <v>11.7</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="27">
         <v>4.13</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="25" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       <c r="I18" s="28">
         <v>6.33</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="27">
         <v>4.47</v>
       </c>
       <c r="K18" s="29" t="s">
@@ -1589,125 +1589,125 @@
         <v>-5.2</v>
       </c>
       <c r="G3" s="9">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="H3" s="9">
         <v>3.2</v>
       </c>
-      <c r="I3" s="12">
-        <v>4.8</v>
+      <c r="I3" s="8">
+        <v>9.6</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-5.2</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>-8.5</v>
       </c>
-      <c r="G4" s="13">
-        <v>0.17</v>
-      </c>
-      <c r="H4" s="13">
+      <c r="G4" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="12">
         <v>3.3</v>
       </c>
       <c r="I4" s="8">
-        <v>19.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>-8.5</v>
       </c>
-      <c r="F5" s="16">
-        <v>-12.3</v>
-      </c>
-      <c r="G5" s="16">
+      <c r="F5" s="15">
+        <v>-17.3</v>
+      </c>
+      <c r="G5" s="15">
         <v>1.17</v>
       </c>
-      <c r="H5" s="16">
-        <v>3.8</v>
-      </c>
-      <c r="I5" s="12">
-        <v>3.26</v>
+      <c r="H5" s="15">
+        <v>8.8</v>
+      </c>
+      <c r="I5" s="8">
+        <v>7.54</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
-        <v>-12.3</v>
-      </c>
-      <c r="F6" s="19">
+      <c r="E6" s="18">
+        <v>-17.3</v>
+      </c>
+      <c r="F6" s="18">
         <v>-22.5</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>0.58</v>
       </c>
-      <c r="H6" s="19">
-        <v>10.2</v>
+      <c r="H6" s="18">
+        <v>5.2</v>
       </c>
       <c r="I6" s="8">
-        <v>17.49</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="21">
         <v>-22.5</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
         <v>-26.5</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="21">
         <v>0.75</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <v>4</v>
       </c>
       <c r="I7" s="8">
@@ -1715,31 +1715,31 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="24">
         <v>-26.5</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="24">
         <v>-38.2</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="24">
         <v>2.83</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="24">
         <v>11.7</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="27">
         <v>4.13</v>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       <c r="H9" s="28">
         <v>6.33</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="27">
         <v>4.47</v>
       </c>
     </row>
